--- a/data/shortlisted_J0001.xlsx
+++ b/data/shortlisted_J0001.xlsx
@@ -503,12 +503,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C0002</t>
+          <t>C0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anita Verma</t>
+          <t>Rahul Sharma</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -516,51 +516,51 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yashwanth9182444@gmail.com</t>
+          <t>yashwanthdevangam@gmail.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anita Verma Frontend Developer | 2 Years Experience Location: Hyderabad Summary: Frontend Developer specializing in Angular and responsive UI design. Skills: Angular, JavaScript, HTML, CSS, Bootstrap Experience: Frontend Developer – UIWorks (2023–Present) - Developed Angular dashboards - Improved UI performance Projects: - Portfolio Website - Admin  dashboard Education:B.Tech in Information Technology</t>
+          <t>Rahul Sharma Data Scientist | 3 Years Experience Location: Bangalore Professional Summary: Data Scientist with 3 years of experience in machine learning and NLP. Strong background in building predictive models and text classification systems. Technical Skills: Python, Machine Learning, NLP, TensorFlow, Scikit-learn, Pandas Work Experience:Data Scientist – XYZ Analytics (2022–Present) - Built NLP models for sentiment analysis - Improved model accuracy by 18% Projects:- Resume Classification System - Chatbot using Transformers Education:B.Tech in Computer Science Engineering Preferred Role: Data Scientist</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Angular,JavaScript,HTML,CSS</t>
+          <t>Python,Machine Learning,NLP,TensorFlow</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>B.Tech IT</t>
+          <t>B.Tech CSE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Candidate meets all the strict criteria for the frontend developer role.</t>
+          <t>Candidate meets all the strict criteria: relevant skills, sufficient experience, located in Bangalore, and expected salary is not mentioned.</t>
         </is>
       </c>
     </row>
